--- a/2 Output/cluster/tables/Table_C0_sample_integrity.xlsx
+++ b/2 Output/cluster/tables/Table_C0_sample_integrity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="62" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="124" uniqueCount="49">
   <si>
     <t>section</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>Expanded model may be used later as a sensitivity or richer segmentation specification.</t>
+  </si>
+  <si>
+    <t>Configured coded analytical dataset; see the project setup and data availability documentation.</t>
   </si>
 </sst>
 </file>
@@ -250,7 +253,7 @@
         <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
